--- a/artfynd/A 9154-2026 artfynd.xlsx
+++ b/artfynd/A 9154-2026 artfynd.xlsx
@@ -12774,7 +12774,7 @@
         <v>131809073</v>
       </c>
       <c r="B113" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
